--- a/output/TA_Monitor_Selezione_HR_Roma_2026-03-15.xlsx
+++ b/output/TA_Monitor_Selezione_HR_Roma_2026-03-15.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Posizioni" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Posizioni'!$A$1:$I$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Posizioni'!$A$1:$I$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -497,12 +497,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Animatore turistico/animatrice turistica</t>
+          <t>Ingegnere/Architetto Tender Specialist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Entertainment Dance</t>
+          <t>Saturno Consulting HR</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -512,36 +512,36 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Viterbo, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>parttime, fulltime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9e882f75a5617d9a</t>
+          <t>https://it.indeed.com/viewjob?jk=057f40c23a96b33b</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Event Manager</t>
+          <t>Optical Technical Project Manager</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cento per Centro S.r.l.</t>
+          <t>Terna</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -551,36 +551,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rieti, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>parttime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=fb648027dd3021c7</t>
+          <t>https://it.indeed.com/viewjob?jk=41451cf3b33375bb</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
+          <t>Ingegnere Meccanico DL e Progettazione</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Saturno Consulting HR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -590,7 +586,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -602,24 +598,24 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=49235986d2cf6301</t>
+          <t>https://it.indeed.com/viewjob?jk=e35f0347ad252e7e</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
+          <t>Project Planner e Controller</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Terna</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -629,36 +625,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=bd1b3e59c44ec5bb</t>
+          <t>https://it.indeed.com/viewjob?jk=2a33a0c2a06a8a50</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HR Business Partner, EU One PXT</t>
+          <t>Direttore Tecnico Cantieri Verde Pubblico</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Saturno Consulting HR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -680,50 +672,58 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=451c1165395cdd9c</t>
+          <t>https://it.indeed.com/viewjob?jk=5a47745206230804</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LUISS meets Generali - Recruiting Day</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Agenzia Generali Roma Corso Trieste</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4383639535</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=86f0a0a875b60568</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
+          <t>Colleferro, LAZ, IT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -750,24 +750,24 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=22a1ddf420e0d824</t>
+          <t>https://it.indeed.com/viewjob?jk=8e8a6819a3bfb95c</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
+          <t>Senior SAP BTP &amp; AI Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -789,12 +789,12 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=e6cf390409a2cf78</t>
+          <t>https://it.indeed.com/viewjob?jk=ee4ec82da870e1de</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-15</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=727f9bebb7430afb</t>
+          <t>https://it.indeed.com/viewjob?jk=056e07e3d7c45fe7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -840,12 +840,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Addetto/a vendite Part time - Outlet Castel Romano</t>
+          <t>Animatore turistico/animatrice turistica</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Skechers</t>
+          <t>Entertainment Dance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -855,36 +855,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Viterbo, LAZ, IT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>parttime, fulltime</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f96e50d1e6879e04</t>
+          <t>https://it.indeed.com/viewjob?jk=9e882f75a5617d9a</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Addetto/a all’ufficio avanzamento del Centro di Eccellenza Meccanico</t>
+          <t>Event Manager</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Cento per Centro S.r.l.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -894,32 +894,36 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cisterna di Latina, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>Rieti, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=66b8c7691cd359f2</t>
+          <t>https://it.indeed.com/viewjob?jk=fb648027dd3021c7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Responsabile Technical Procurement</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ITA airways</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -929,32 +933,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fiumicino, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=99039b787e45436a</t>
+          <t>https://it.indeed.com/viewjob?jk=49235986d2cf6301</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MEDICO DI REPARTO - M/F</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KORIAN</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -964,32 +972,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Campagnano di Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Colleferro, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=72afea7f6212e0e6</t>
+          <t>https://it.indeed.com/viewjob?jk=bd1b3e59c44ec5bb</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Progettista meccanico</t>
+          <t>HR Business Partner, EU One PXT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PROGER</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1011,34 +1023,34 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=155bafc2ad9a4f55</t>
+          <t>https://it.indeed.com/viewjob?jk=451c1165395cdd9c</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Assistente al Coordinatore Clinico</t>
+          <t>LUISS meets Generali - Recruiting Day</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tutti giù per terra Onlus</t>
+          <t>Agenzia Generali Roma Corso Trieste</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Rome, Latium, Italy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1046,24 +1058,20 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=353770ee335e013b</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4383639535</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stagista Help Desk - Roma</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BONELLI EREDE PAPPALARDO</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1073,36 +1081,36 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Passo Corese, LAZ, IT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=27b3108f7567db7a</t>
+          <t>https://it.indeed.com/viewjob?jk=22a1ddf420e0d824</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Addetti alle vendite</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pilato Store</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1112,34 +1120,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Colleferro, LAZ, IT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>parttime, fulltime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=4f9917c9f4eff5f9</t>
+          <t>https://it.indeed.com/viewjob?jk=e6cf390409a2cf78</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Responsabile Di Negozio</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>HR Business Partner, EU One PXT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>indeed</t>
@@ -1150,29 +1162,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=ff5fafbeb3752b08</t>
+          <t>https://it.indeed.com/viewjob?jk=727f9bebb7430afb</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Architetto Infrastrutturale</t>
+          <t>Addetto/a vendite Part time - Outlet Castel Romano</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Skechers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1185,12 +1201,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=215e2625f80dfca1</t>
+          <t>https://it.indeed.com/viewjob?jk=f96e50d1e6879e04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1202,12 +1222,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Addetto/a servizi mensa</t>
+          <t>Addetto/a all’ufficio avanzamento del Centro di Eccellenza Meccanico</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NHRG SRL – Agenzia per il Lavoro</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1217,19 +1237,15 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rieti, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>parttime</t>
-        </is>
-      </c>
+          <t>Cisterna di Latina, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=2f63182ded1e797e</t>
+          <t>https://it.indeed.com/viewjob?jk=66b8c7691cd359f2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1241,12 +1257,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Junior PMO Pubblica Amministrazione</t>
+          <t>Responsabile Technical Procurement</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>ITA airways</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1256,7 +1272,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Fiumicino, LAZ, IT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1264,7 +1280,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=56f8f83b3dbc221e</t>
+          <t>https://it.indeed.com/viewjob?jk=99039b787e45436a</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1276,12 +1292,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Animatori per bambini e ragazzi in soggiorni residenziali</t>
+          <t>MEDICO DI REPARTO - M/F</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DOC s.c.s.</t>
+          <t>KORIAN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1291,19 +1307,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Campagnano di Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=2379cce56a434871</t>
+          <t>https://it.indeed.com/viewjob?jk=72afea7f6212e0e6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1315,12 +1327,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lavoro a ROMA - COLLOQUIO IN sede BARBERINI</t>
+          <t>Progettista meccanico</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Globe MKD</t>
+          <t>PROGER</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1333,12 +1345,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=5ca7c4c08a45923f</t>
+          <t>https://it.indeed.com/viewjob?jk=155bafc2ad9a4f55</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1350,12 +1366,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Assistente al Coordinatore Clinico</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Terna</t>
+          <t>Tutti giù per terra Onlus</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1373,55 +1389,63 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=b05d2a6aa42288f0</t>
+          <t>https://it.indeed.com/viewjob?jk=353770ee335e013b</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Impiegato/a Risorse Umane | Consulenze</t>
+          <t>Stagista Help Desk - Roma</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>key-absolute</t>
+          <t>BONELLI EREDE PAPPALARDO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4384261319</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=27b3108f7567db7a</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
+          <t>Addetti alle vendite</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Pilato Store</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1431,38 +1455,34 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime, fulltime</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9458a38ff98817fa</t>
+          <t>https://it.indeed.com/viewjob?jk=4f9917c9f4eff5f9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Amazon.com</t>
-        </is>
-      </c>
+          <t>Responsabile Di Negozio</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>indeed</t>
@@ -1470,36 +1490,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=a51f253cfb43e8ad</t>
+          <t>https://it.indeed.com/viewjob?jk=ff5fafbeb3752b08</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Programme Officer – Global Rapid Response Team (Access &amp; HMI Specialist)</t>
+          <t>Architetto Infrastrutturale</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>World Food Programme</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1512,16 +1528,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=2b0c5fc77486f46c</t>
+          <t>https://it.indeed.com/viewjob?jk=215e2625f80dfca1</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1533,12 +1545,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Junior School Class Teacher</t>
+          <t>Addetto/a servizi mensa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>St George's British International School</t>
+          <t>NHRG SRL – Agenzia per il Lavoro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1548,19 +1560,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Rieti, LAZ, IT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=2e3868f91731b8bc</t>
+          <t>https://it.indeed.com/viewjob?jk=2f63182ded1e797e</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1572,12 +1584,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HR Business Partner, EU One PXT</t>
+          <t>Junior PMO Pubblica Amministrazione</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1590,33 +1602,29 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=64a42c84f116d4d6</t>
+          <t>https://it.indeed.com/viewjob?jk=56f8f83b3dbc221e</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HR Generalist (Categorie Protette L.68/99)</t>
+          <t>Animatori per bambini e ragazzi in soggiorni residenziali</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FILMMASTER</t>
+          <t>DOC s.c.s.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1638,7 +1646,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9bb6d72ced10d28a</t>
+          <t>https://it.indeed.com/viewjob?jk=2379cce56a434871</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1650,12 +1658,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HR Clerk - maternity cover</t>
+          <t>Lavoro a ROMA - COLLOQUIO IN sede BARBERINI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Globe MKD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1668,16 +1676,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=cf06994c867d9dde</t>
+          <t>https://it.indeed.com/viewjob?jk=5ca7c4c08a45923f</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1689,22 +1693,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CLIENT RECRUITMENT SPECIALIST ON SITE</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Gi Group</t>
+          <t>Terna</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1712,59 +1716,55 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4383146711</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=b05d2a6aa42288f0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HR Talent Support Intern</t>
+          <t>Impiegato/a Risorse Umane | Consulenze</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ayvens</t>
+          <t>key-absolute</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=1893b6c166669e55</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4384261319</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Conferimento dell'incarico di durata minima quinquennale di direttore della UOC Pediatria - Presidio ospedaliero Sant'Eugenio.</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AZIENDA SANITARIA LOCALE ROMA 2 DI ROMA</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1774,32 +1774,36 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=badb6c12cf044f4b</t>
+          <t>https://it.indeed.com/viewjob?jk=9458a38ff98817fa</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hotel Manager | VOI Andilana Beach Resort – Nosy Be (Madagascar)</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VOIhotels</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1809,32 +1813,36 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>Colleferro, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=d20f736ff858e2e1</t>
+          <t>https://it.indeed.com/viewjob?jk=a51f253cfb43e8ad</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Specialist - Roma</t>
+          <t>Programme Officer – Global Rapid Response Team (Access &amp; HMI Specialist)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>World Food Programme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1847,29 +1855,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=1029f9f8e3ed7ace</t>
+          <t>https://it.indeed.com/viewjob?jk=2b0c5fc77486f46c</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CORPORATE ACCELERATING PARTNERSHIP IMPACT SPECIALIST</t>
+          <t>Junior School Class Teacher</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Save the Children</t>
+          <t>St George's British International School</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1882,29 +1894,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=ff9f346ee9e94cdd</t>
+          <t>https://it.indeed.com/viewjob?jk=2e3868f91731b8bc</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nuova Selezione: Attività Lun - Ven</t>
+          <t>HR Business Partner, EU One PXT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Globe MKD</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1919,31 +1935,31 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=74affdc12247cbe4</t>
+          <t>https://it.indeed.com/viewjob?jk=64a42c84f116d4d6</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sales Assistant - art. 18 Legge 68/99 - ROMA CC Euroma2</t>
+          <t>HR Generalist (Categorie Protette L.68/99)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LA CASA DE LAS CARCASAS</t>
+          <t>FILMMASTER</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1958,31 +1974,31 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=4cd1c62895374a74</t>
+          <t>https://it.indeed.com/viewjob?jk=9bb6d72ced10d28a</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>International Tax Manager</t>
+          <t>HR Clerk - maternity cover</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Assist Digital</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1995,68 +2011,64 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f2d42049ad345b64</t>
+          <t>https://it.indeed.com/viewjob?jk=cf06994c867d9dde</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Educatrice/Educatore</t>
+          <t>CLIENT RECRUITMENT SPECIALIST ON SITE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NS12 S.p.A.</t>
+          <t>Gi Group</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=8f824306f45ed16b</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4383146711</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Commerciali</t>
+          <t>HR Talent Support Intern</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Ayvens</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2069,29 +2081,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=64ea4b8ebf873073</t>
+          <t>https://it.indeed.com/viewjob?jk=1893b6c166669e55</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ingegnere Civile</t>
+          <t>Conferimento dell'incarico di durata minima quinquennale di direttore della UOC Pediatria - Presidio ospedaliero Sant'Eugenio.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>AZIENDA SANITARIA LOCALE ROMA 2 DI ROMA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2109,24 +2125,24 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=44239534262fd727</t>
+          <t>https://it.indeed.com/viewjob?jk=badb6c12cf044f4b</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tecnico specializzato (CND)</t>
+          <t>Hotel Manager | VOI Andilana Beach Resort – Nosy Be (Madagascar)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>VOIhotels</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2136,7 +2152,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Rocca Priora, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2144,7 +2160,7 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3ba1adc13ca58b04</t>
+          <t>https://it.indeed.com/viewjob?jk=d20f736ff858e2e1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2156,12 +2172,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Addetto Customer Care (part-time o full-time)</t>
+          <t>Specialist - Roma</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2174,16 +2190,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>parttime, fulltime</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=c2c877fe0af58701</t>
+          <t>https://it.indeed.com/viewjob?jk=1029f9f8e3ed7ace</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2195,12 +2207,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Montatore/trice di arredi</t>
+          <t>CORPORATE ACCELERATING PARTNERSHIP IMPACT SPECIALIST</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Save the Children</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2213,16 +2225,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=7ad8b4b1e93c3ae8</t>
+          <t>https://it.indeed.com/viewjob?jk=ff9f346ee9e94cdd</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2234,12 +2242,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Security analyst</t>
+          <t>Nuova Selezione: Attività Lun - Ven</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Globe MKD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2252,12 +2260,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=cd1bff3da20c2a29</t>
+          <t>https://it.indeed.com/viewjob?jk=74affdc12247cbe4</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2269,12 +2281,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Addetto/a Controllo Qualità</t>
+          <t>Sales Assistant - art. 18 Legge 68/99 - ROMA CC Euroma2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>LA CASA DE LAS CARCASAS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2284,15 +2296,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pomezia, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=279e25071867d71e</t>
+          <t>https://it.indeed.com/viewjob?jk=4cd1c62895374a74</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2304,12 +2320,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Assuntore/trice rischi assicurativi junior</t>
+          <t>International Tax Manager</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Assist Digital</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2319,7 +2335,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Latina, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
@@ -2327,7 +2343,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9c1dca820c28143e</t>
+          <t>https://it.indeed.com/viewjob?jk=f2d42049ad345b64</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2339,12 +2355,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Impiegato/a Assicurativo</t>
+          <t>Educatrice/Educatore</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>NS12 S.p.A.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2354,15 +2370,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Latina, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=61fef49bb0dd7189</t>
+          <t>https://it.indeed.com/viewjob?jk=8f824306f45ed16b</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2374,12 +2394,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Front Office Manager</t>
+          <t>Commerciali</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Palazzo Montemartini Rome</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2392,16 +2412,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=97457b54fb0d5864</t>
+          <t>https://it.indeed.com/viewjob?jk=64ea4b8ebf873073</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2413,12 +2429,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Operatore Elettrotermico</t>
+          <t>Ingegnere Civile</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2436,7 +2452,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=d077b942ffc8a312</t>
+          <t>https://it.indeed.com/viewjob?jk=44239534262fd727</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2448,12 +2464,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DISPONENTE / IMPIEGATO OPERATIVO TRASPORTI</t>
+          <t>Tecnico specializzato (CND)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2463,7 +2479,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Rocca Priora, LAZ, IT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2471,7 +2487,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=45a7dcb9aa87f56e</t>
+          <t>https://it.indeed.com/viewjob?jk=3ba1adc13ca58b04</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2483,12 +2499,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Addetto/a Ufficio Ordini</t>
+          <t>Addetto Customer Care (part-time o full-time)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2501,12 +2517,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>parttime, fulltime</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=20cbece5511664b3</t>
+          <t>https://it.indeed.com/viewjob?jk=c2c877fe0af58701</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2518,43 +2538,51 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Impiegato/a Risorse Umane - Servizi per Privati e Imprese</t>
+          <t>Montatore/trice di arredi</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cosma-sol</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Frosinone, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4383938857</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=7ad8b4b1e93c3ae8</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
+          <t>Security analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2564,36 +2592,32 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=4b1a5bc701ec99d0</t>
+          <t>https://it.indeed.com/viewjob?jk=cd1bff3da20c2a29</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
+          <t>Addetto/a Controllo Qualità</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2603,46 +2627,42 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Pomezia, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=2e950b6a1ceb8799</t>
+          <t>https://it.indeed.com/viewjob?jk=279e25071867d71e</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Remote Recruiter (Freelance / Solo / Independent)</t>
+          <t>Assuntore/trice rischi assicurativi junior</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Construction Index Ltd</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Latina, LAZ, IT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr"/>
@@ -2650,20 +2670,24 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4385127372</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=9c1dca820c28143e</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HR Business Partner, EU One PXT</t>
+          <t>Impiegato/a Assicurativo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2673,36 +2697,32 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Latina, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3a856ec1accadb1f</t>
+          <t>https://it.indeed.com/viewjob?jk=61fef49bb0dd7189</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Addetto/a Gestione del Personale</t>
+          <t>Front Office Manager</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pewex</t>
+          <t>Palazzo Montemartini Rome</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2717,14 +2737,14 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>fulltime, internship</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=0c283fbd8bb16d36</t>
+          <t>https://it.indeed.com/viewjob?jk=97457b54fb0d5864</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -2736,7 +2756,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HR Generalist</t>
+          <t>Operatore Elettrotermico</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2759,7 +2779,7 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=43e3e64850df4b52</t>
+          <t>https://it.indeed.com/viewjob?jk=d077b942ffc8a312</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -2771,12 +2791,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Talent and Performance, D&amp;I Manager</t>
+          <t>DISPONENTE / IMPIEGATO OPERATIVO TRASPORTI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2789,16 +2809,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=b0a5a75089f9aabb</t>
+          <t>https://it.indeed.com/viewjob?jk=45a7dcb9aa87f56e</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -2810,22 +2826,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Addetto/a Risorse Umane - Selezione e gestione del personale</t>
+          <t>Addetto/a Ufficio Ordini</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>To Be Service srl</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -2833,59 +2849,55 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4383941771</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=20cbece5511664b3</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Customer Success Specialist GP</t>
+          <t>Impiegato/a Risorse Umane - Servizi per Privati e Imprese</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DocPlanner</t>
+          <t>Cosma-sol</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Frosinone, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=938ecc7ed1c24abe</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4383938857</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BRAND MANAGER - International brands</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Peroni</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2895,32 +2907,36 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=678d68ae4243e946</t>
+          <t>https://it.indeed.com/viewjob?jk=4b1a5bc701ec99d0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chef - NH Collection Roma Giustiniano</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Minor Hotels Europe &amp; Americas</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2930,102 +2946,106 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Colleferro, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=da578a37418f6b15</t>
+          <t>https://it.indeed.com/viewjob?jk=2e950b6a1ceb8799</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Stock Coordinator - Castel Romano Designer Outlet</t>
+          <t>Remote Recruiter (Freelance / Solo / Independent)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>RITUALS COSMETICS</t>
+          <t>The Construction Index Ltd</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>parttime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=fac2ecc40fae915b</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4385127372</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HR Director</t>
+          <t>HR Business Partner, EU One PXT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Randstad Professional Italia</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4384153732</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=3a856ec1accadb1f</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Welfare&amp;Wellbeing Expert</t>
+          <t>Addetto/a Gestione del Personale</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Pewex</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3038,39 +3058,43 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>fulltime, internship</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=01b6b45d59b07af2</t>
+          <t>https://it.indeed.com/viewjob?jk=0c283fbd8bb16d36</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Addetto/a Risorse Umane - Settore Caffè</t>
+          <t>HR Generalist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EmmeBi Group</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
@@ -3078,20 +3102,24 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4384170611</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=43e3e64850df4b52</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Buyer / Addetto agli Acquisti</t>
+          <t>Talent and Performance, D&amp;I Manager</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Smo-King</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3113,34 +3141,34 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=7c020459d9d87757</t>
+          <t>https://it.indeed.com/viewjob?jk=b0a5a75089f9aabb</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LGS - Anagni - Junior Facility Management</t>
+          <t>Addetto/a Risorse Umane - Selezione e gestione del personale</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>To Be Service srl</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Anagni, LAZ, IT</t>
+          <t>Rome, Latium, Italy</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
@@ -3148,24 +3176,20 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=c1a63beb652035f7</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4383941771</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Beauty Advisor - Latina</t>
+          <t>Customer Success Specialist GP</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sephora</t>
+          <t>DocPlanner</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3175,32 +3199,36 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Latina, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=a08c4aafa5552071</t>
+          <t>https://it.indeed.com/viewjob?jk=938ecc7ed1c24abe</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Junior GIS Specialist – Servizi Territorio e Ambiente per la Pubblica Amministrazione</t>
+          <t>BRAND MANAGER - International brands</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kibernetes</t>
+          <t>Peroni</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3213,33 +3241,29 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=53be9235ea6845d5</t>
+          <t>https://it.indeed.com/viewjob?jk=678d68ae4243e946</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ingegneri/re progettisti/ste.</t>
+          <t>Chef - NH Collection Roma Giustiniano</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Aero Sekur S.p.A.</t>
+          <t>Minor Hotels Europe &amp; Americas</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3249,36 +3273,32 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Aprilia, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=7a0b536c9dc34de1</t>
+          <t>https://it.indeed.com/viewjob?jk=da578a37418f6b15</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PM con esperienza</t>
+          <t>Stock Coordinator - Castel Romano Designer Outlet</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Aero Sekur S.p.A.</t>
+          <t>RITUALS COSMETICS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3288,19 +3308,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Aprilia, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=791e1397aaa11c4f</t>
+          <t>https://it.indeed.com/viewjob?jk=fac2ecc40fae915b</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3312,51 +3332,43 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Specialista Verifica e Controllo Posizioni (Ambito Tributi Locali IMU - TARI)</t>
+          <t>HR Director</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Kibernetes</t>
+          <t>Randstad Professional Italia</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=6c738fd1e7bcb0bc</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4384153732</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Progettista Elettronico RF junior</t>
+          <t>Welfare&amp;Wellbeing Expert</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3374,7 +3386,7 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=c1134133e5ab2275</t>
+          <t>https://it.indeed.com/viewjob?jk=01b6b45d59b07af2</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3386,22 +3398,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>System Administration specialist full remote</t>
+          <t>Addetto/a Risorse Umane - Settore Caffè</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>EmmeBi Group</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Rome, Latium, Italy</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -3409,24 +3421,20 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=18e901403e505b30</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4384170611</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sales Advisor  | Contratto a Chiamata | Castel Romano</t>
+          <t>Buyer / Addetto agli Acquisti</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>H&amp;M</t>
+          <t>Smo-King</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3448,7 +3456,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f68dcb131d4b430c</t>
+          <t>https://it.indeed.com/viewjob?jk=7c020459d9d87757</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3460,12 +3468,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Reservations Agent - Appartenente alle Categorie Protette- Villa Agrippina (38730)</t>
+          <t>LGS - Anagni - Junior Facility Management</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Meliá Hotels International</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3475,19 +3483,15 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>parttime</t>
-        </is>
-      </c>
+          <t>Anagni, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=fa307ef6d6f66bee</t>
+          <t>https://it.indeed.com/viewjob?jk=c1a63beb652035f7</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -3499,12 +3503,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Addetti Back Office Settore Auto Roma</t>
+          <t>Beauty Advisor - Latina</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Concessionaria Fiori</t>
+          <t>Sephora</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3514,19 +3518,15 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Latina, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=64e456ef234ef9d4</t>
+          <t>https://it.indeed.com/viewjob?jk=a08c4aafa5552071</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -3538,12 +3538,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>EVENTI FIERE NEGOZI CONCERTI ||| Personale ROMA</t>
+          <t>Junior GIS Specialist – Servizi Territorio e Ambiente per la Pubblica Amministrazione</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Globe MKD</t>
+          <t>Kibernetes</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3558,14 +3558,14 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>fulltime, internship</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=eec4e11daac0968b</t>
+          <t>https://it.indeed.com/viewjob?jk=53be9235ea6845d5</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -3577,12 +3577,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Addetto/a Vendite profilo ESPERTO</t>
+          <t>Ingegneri/re progettisti/ste.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Aero Sekur S.p.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Aprilia, LAZ, IT</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3604,7 +3604,7 @@
       <c r="G86" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=5a8633b689ba60ba</t>
+          <t>https://it.indeed.com/viewjob?jk=7a0b536c9dc34de1</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -3616,12 +3616,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tecnico Collaudatore</t>
+          <t>PM con esperienza</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Aero Sekur S.p.A.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3631,15 +3631,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>Aprilia, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=d5aac9fbe01c0617</t>
+          <t>https://it.indeed.com/viewjob?jk=791e1397aaa11c4f</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -3651,12 +3655,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IMPIEGATO UFFICIO ACQUISTI</t>
+          <t>Specialista Verifica e Controllo Posizioni (Ambito Tributi Locali IMU - TARI)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>APIS Srl Agenzia per il Lavoro</t>
+          <t>Kibernetes</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3666,7 +3670,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Formello, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3678,7 +3682,7 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=bbd1e991d3302a43</t>
+          <t>https://it.indeed.com/viewjob?jk=6c738fd1e7bcb0bc</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -3690,49 +3694,57 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Paghe e contributi risorse umane</t>
+          <t>Progettista Elettronico RF junior</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>STAFF Agenzia per il Lavoro</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4384172751</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=c1134133e5ab2275</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HR Business Partner Specialist</t>
+          <t>System Administration specialist full remote</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Multiversity Group</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -3740,20 +3752,24 @@
       <c r="G90" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4382577692</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=18e901403e505b30</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
+          <t>Sales Advisor  | Contratto a Chiamata | Castel Romano</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>H&amp;M</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3763,7 +3779,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3775,24 +3791,24 @@
       <c r="G91" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=65a08402297d784d</t>
+          <t>https://it.indeed.com/viewjob?jk=f68dcb131d4b430c</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Strategy &amp; Transformation Analyst Consultant</t>
+          <t>Reservations Agent - Appartenente alle Categorie Protette- Villa Agrippina (38730)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Meliá Hotels International</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3805,29 +3821,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3cdb921cbbee5031</t>
+          <t>https://it.indeed.com/viewjob?jk=fa307ef6d6f66bee</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
+          <t>Addetti Back Office Settore Auto Roma</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Concessionaria Fiori</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3837,7 +3857,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3849,24 +3869,24 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f31360bb619dffe9</t>
+          <t>https://it.indeed.com/viewjob?jk=64e456ef234ef9d4</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BIM Consultant – Categoria Protetta L.68/99</t>
+          <t>EVENTI FIERE NEGOZI CONCERTI ||| Personale ROMA</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BIP</t>
+          <t>Globe MKD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3881,31 +3901,31 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>fulltime, internship</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=44a097839850db18</t>
+          <t>https://it.indeed.com/viewjob?jk=eec4e11daac0968b</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Process &amp; Reporting Analyst – Categoria Protetta L.68/99</t>
+          <t>Addetto/a Vendite profilo ESPERTO</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BIP</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3927,34 +3947,34 @@
       <c r="G95" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=0ca7f0af055bc26c</t>
+          <t>https://it.indeed.com/viewjob?jk=5a8633b689ba60ba</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>HR Recruiter (Chinese-speaking)</t>
+          <t>Tecnico Collaudatore</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GOFO</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -3962,129 +3982,121 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4383229094</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=d5aac9fbe01c0617</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Head of Tech Talent &amp; Employer Branding</t>
+          <t>IMPIEGATO UFFICIO ACQUISTI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Exein</t>
+          <t>APIS Srl Agenzia per il Lavoro</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>Formello, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4382877550</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=bbd1e991d3302a43</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HR Business Partner, EU One PXT</t>
+          <t>Paghe e contributi risorse umane</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>STAFF Agenzia per il Lavoro</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9aef46467d2d5ce0</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4384172751</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ADDETTA/O UFFICIO GESTIONE DEL PERSONALE - Categorie Protette (L. 68/99)</t>
+          <t>HR Business Partner Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>R&amp;A Holding S.r.l.</t>
+          <t>Multiversity Group</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=6bb2a7a43c16c03f</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4382577692</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Talent Management Specialist</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Seargin</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -4094,42 +4106,46 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=c5dc1b040b057ec7</t>
+          <t>https://it.indeed.com/viewjob?jk=65a08402297d784d</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>HCM Operations &amp; Talent Director - ICT &amp; Digital Sector Markets</t>
+          <t>Strategy &amp; Transformation Analyst Consultant</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Humanativa Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -4137,51 +4153,63 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4382586675</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=3cdb921cbbee5031</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HR Generalist Apprentice</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Arsenale Group</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>Colleferro, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4383736694</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=f31360bb619dffe9</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ADDETTI / ADDETTE DATA ENTRY – PROGETTO TEMPORANEO (4 SETTIMANE) ROMA EUR</t>
+          <t>BIM Consultant – Categoria Protetta L.68/99</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Solgeko Srl</t>
+          <t>BIP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -4194,12 +4222,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=8b6d065ddfeec006</t>
+          <t>https://it.indeed.com/viewjob?jk=44a097839850db18</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4211,12 +4243,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sales Assistant</t>
+          <t>Process &amp; Reporting Analyst – Categoria Protetta L.68/99</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Il Lanificio</t>
+          <t>BIP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4226,19 +4258,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Valmontone, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=a8440493d8215086</t>
+          <t>https://it.indeed.com/viewjob?jk=0ca7f0af055bc26c</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -4250,22 +4282,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Radar &amp; ATC System Integrator Specialist</t>
+          <t>HR Recruiter (Chinese-speaking)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Enav</t>
+          <t>GOFO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Rome, Latium, Italy</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
@@ -4273,63 +4305,51 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f40740794677e980</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4383229094</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Responsabile operativa, zona Viale Libia, Roma</t>
+          <t>Head of Tech Talent &amp; Employer Branding</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CONSORZIO STABILE LGA SERVICE</t>
+          <t>Exein</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=363ea67eb7afb7f7</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4382877550</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Housekeeper zona Parioli, Roma</t>
+          <t>HR Business Partner, EU One PXT</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>CONSORZIO STABILE LGA SERVICE</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4351,24 +4371,24 @@
       <c r="G107" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=97216e2ab708bb65</t>
+          <t>https://it.indeed.com/viewjob?jk=9aef46467d2d5ce0</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Assemblatore	rice meccanicoa</t>
+          <t>ADDETTA/O UFFICIO GESTIONE DEL PERSONALE - Categorie Protette (L. 68/99)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Istituto G. Meschini</t>
+          <t>R&amp;A Holding S.r.l.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -4378,36 +4398,36 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Anzio, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=32884f68490331f1</t>
+          <t>https://it.indeed.com/viewjob?jk=6bb2a7a43c16c03f</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Tirocinante Pizzaioloa</t>
+          <t>Talent Management Specialist</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Istituto G. Meschini</t>
+          <t>Seargin</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4417,114 +4437,94 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Albano Laziale, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=dadbe338dff0e9b2</t>
+          <t>https://it.indeed.com/viewjob?jk=c5dc1b040b057ec7</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>TIROCINANTE ADDETTOA IMBALLAGGIO</t>
+          <t>HCM Operations &amp; Talent Director - ICT &amp; Digital Sector Markets</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Istituto G. Meschini</t>
+          <t>Humanativa Group</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Pomezia, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=54ab95c28f3b5e42</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4382586675</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Addetto/a Vendite Pacchetti Turistici</t>
+          <t>HR Generalist Apprentice</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Arsenale Group</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=aa92578a40efeaff</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4383736694</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Addetto/a Vendite profilo NEOFITA</t>
+          <t>ADDETTI / ADDETTE DATA ENTRY – PROGETTO TEMPORANEO (4 SETTIMANE) ROMA EUR</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Solgeko Srl</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -4537,16 +4537,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>internship</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=73b0d89f12d25734</t>
+          <t>https://it.indeed.com/viewjob?jk=8b6d065ddfeec006</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -4558,12 +4554,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Operatore d’ufficio con competenze informatiche e CAD</t>
+          <t>Sales Assistant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Il Lanificio</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4573,15 +4569,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>Valmontone, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=cc4998d3af3133ac</t>
+          <t>https://it.indeed.com/viewjob?jk=a8440493d8215086</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -4593,12 +4593,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Responsabile Ufficio Calibrazione</t>
+          <t>Radar &amp; ATC System Integrator Specialist</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Enav</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -4616,7 +4616,7 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=4bc63cd64dab0aa6</t>
+          <t>https://it.indeed.com/viewjob?jk=f40740794677e980</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -4628,12 +4628,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>n. 1 Referente giuridico - amministrativo _ Roma_</t>
+          <t>Responsabile operativa, zona Viale Libia, Roma</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Agenzia Demanio</t>
+          <t>CONSORZIO STABILE LGA SERVICE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4646,27 +4646,35 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9392a531c0f06262</t>
+          <t>https://it.indeed.com/viewjob?jk=363ea67eb7afb7f7</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Event Manager</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
+          <t>Housekeeper zona Parioli, Roma</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>CONSORZIO STABILE LGA SERVICE</t>
+        </is>
+      </c>
       <c r="C116" t="inlineStr">
         <is>
           <t>indeed</t>
@@ -4674,19 +4682,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Rieti, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=fb648027dd3021c7</t>
+          <t>https://it.indeed.com/viewjob?jk=97216e2ab708bb65</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -4698,12 +4706,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Specialista HSE</t>
+          <t>Assemblatore	rice meccanicoa</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Istituto G. Meschini</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4713,15 +4721,19 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>Anzio, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=90f8f74cfab1b8de</t>
+          <t>https://it.indeed.com/viewjob?jk=32884f68490331f1</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -4733,12 +4745,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ASPP</t>
+          <t>Tirocinante Pizzaioloa</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Istituto G. Meschini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4748,15 +4760,19 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>Albano Laziale, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=250961132834bb2a</t>
+          <t>https://it.indeed.com/viewjob?jk=dadbe338dff0e9b2</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -4768,12 +4784,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Assistente Commerciale</t>
+          <t>TIROCINANTE ADDETTOA IMBALLAGGIO</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Istituto G. Meschini</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4783,19 +4799,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Frosinone, LAZ, IT</t>
+          <t>Pomezia, LAZ, IT</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>parttime, fulltime</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=ce30a0e6d84c543e</t>
+          <t>https://it.indeed.com/viewjob?jk=54ab95c28f3b5e42</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -4807,7 +4823,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Addetto/a Front Office</t>
+          <t>Addetto/a Vendite Pacchetti Turistici</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4822,7 +4838,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Frosinone, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4834,7 +4850,7 @@
       <c r="G120" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=ed3f7b7340afe028</t>
+          <t>https://it.indeed.com/viewjob?jk=aa92578a40efeaff</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -4846,12 +4862,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FRESATORE CNC SENIOR</t>
+          <t>Addetto/a Vendite profilo NEOFITA</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>APIS Srl Agenzia per il Lavoro</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4861,15 +4877,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Palestrina, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>internship</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=216c58b689d75017</t>
+          <t>https://it.indeed.com/viewjob?jk=73b0d89f12d25734</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -4881,12 +4901,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Consultant – Sistemi di Pricing &amp; Risk (Murex/Kondor+)</t>
+          <t>Operatore d’ufficio con competenze informatiche e CAD</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>be group</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4904,7 +4924,7 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=0a88874daad6a557</t>
+          <t>https://it.indeed.com/viewjob?jk=cc4998d3af3133ac</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -4916,22 +4936,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>HR MANAGER JUNIOR</t>
+          <t>Responsabile Ufficio Calibrazione</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Italian Design Institute</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -4939,30 +4959,34 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4382019981</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=4bc63cd64dab0aa6</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>HR Specialist – Sistemi Gestione Utenze Domestiche</t>
+          <t>n. 1 Referente giuridico - amministrativo _ Roma_</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EmmeBi Group</t>
+          <t>Agenzia Demanio</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Frosinone, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -4970,22 +4994,22 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4382298747</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=9392a531c0f06262</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Amazon.com</t>
-        </is>
-      </c>
+          <t>Event Manager</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>indeed</t>
@@ -4993,36 +5017,36 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
+          <t>Rieti, LAZ, IT</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=d7b1ac40655c8f48</t>
+          <t>https://it.indeed.com/viewjob?jk=fb648027dd3021c7</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
+          <t>Specialista HSE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -5032,36 +5056,32 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=5c10c47851ef179d</t>
+          <t>https://it.indeed.com/viewjob?jk=90f8f74cfab1b8de</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Intern Library</t>
+          <t>ASPP</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nuova Accademia di Belle Arti</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5074,16 +5094,12 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=35fc8ddfa87736b9</t>
+          <t>https://it.indeed.com/viewjob?jk=250961132834bb2a</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5095,12 +5111,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Engagement Manager, Italy</t>
+          <t>Assistente Commerciale</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -5110,19 +5126,19 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Frosinone, LAZ, IT</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime, fulltime</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=72a49641be0e8959</t>
+          <t>https://it.indeed.com/viewjob?jk=ce30a0e6d84c543e</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -5134,12 +5150,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Marketing Cloud Specialist</t>
+          <t>Addetto/a Front Office</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -5149,7 +5165,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Frosinone, LAZ, IT</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5161,7 +5177,7 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=ab10c1430e4b490b</t>
+          <t>https://it.indeed.com/viewjob?jk=ed3f7b7340afe028</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -5173,22 +5189,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>IYO | Recruiting Tour: Sardegna New Opening | Ali Professional</t>
+          <t>FRESATORE CNC SENIOR</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ali Professional</t>
+          <t>APIS Srl Agenzia per il Lavoro</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Palestrina, LAZ, IT</t>
         </is>
       </c>
       <c r="E130" t="inlineStr"/>
@@ -5196,24 +5212,24 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4375407023</t>
+          <t>https://it.indeed.com/viewjob?jk=216c58b689d75017</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HR Recruiter Assistant L.68/99 - Categoria Protetta Part Time</t>
+          <t>Senior Consultant – Sistemi di Pricing &amp; Risk (Murex/Kondor+)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>BIP</t>
+          <t>be group</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -5226,173 +5242,169 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=de5de5a9624794c6</t>
+          <t>https://it.indeed.com/viewjob?jk=0a88874daad6a557</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HR Business Partner, EU One PXT</t>
+          <t>HR MANAGER JUNIOR</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Italian Design Institute</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3901726c645d39a9</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4382019981</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>HR Specialist</t>
+          <t>HR Specialist – Sistemi Gestione Utenze Domestiche</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Stargate Security srl</t>
+          <t>EmmeBi Group</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Frosinone, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=a580c2c3686cd978</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4382298747</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Talent Acquisition Specialist | Management Consulting &amp; Advisory</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DGS</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4353205273</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=d7b1ac40655c8f48</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Addetto/a selezione e valutazione del Personale</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Adecco</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>Colleferro, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4382072576</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=5c10c47851ef179d</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Talent Acquisition Trainee - Spanish &amp; Italian Market</t>
+          <t>Intern Library</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Nuova Accademia di Belle Arti</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -5407,31 +5419,31 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>internship</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=e69d1c8d88b80162</t>
+          <t>https://it.indeed.com/viewjob?jk=35fc8ddfa87736b9</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t>Engagement Manager, Italy</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Zuma</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -5453,7 +5465,7 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=2d4e53c8f85af891</t>
+          <t>https://it.indeed.com/viewjob?jk=72a49641be0e8959</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -5465,12 +5477,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sommelier</t>
+          <t>Marketing Cloud Specialist</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Zuma</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5492,7 +5504,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f2522d0ac92e7cd8</t>
+          <t>https://it.indeed.com/viewjob?jk=ab10c1430e4b490b</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -5504,51 +5516,47 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Internal AI Tools Specialist - 100% Remote - Europe</t>
+          <t>IYO | Recruiting Tour: Sardegna New Opening | Ali Professional</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Hostaway</t>
+          <t>Ali Professional</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=4eff38852de5985e</t>
+          <t>https://www.linkedin.com/jobs/view/4375407023</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>HR Recruiter Assistant L.68/99 - Categoria Protetta Part Time</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SEGULA Technologies</t>
+          <t>BIP</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5570,24 +5578,24 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=c28fea3f09e2b064</t>
+          <t>https://it.indeed.com/viewjob?jk=de5de5a9624794c6</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Operatore/trice Telefonia Outbound Avezzano</t>
+          <t>HR Business Partner, EU One PXT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>tecnocall srl</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -5597,32 +5605,36 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Avezzano, ABR, IT</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=5e3588ba0550d28f</t>
+          <t>https://it.indeed.com/viewjob?jk=3901726c645d39a9</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Payroll Specialist - Roma Tor Vergata</t>
+          <t>HR Specialist</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SPP Agenzia per il Lavoro</t>
+          <t>Stargate Security srl</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -5644,102 +5656,86 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9339d90893065e7d</t>
+          <t>https://it.indeed.com/viewjob?jk=a580c2c3686cd978</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Addetto IT Service Desk</t>
+          <t>Senior Talent Acquisition Specialist | Management Consulting &amp; Advisory</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Poligrafico e Zecca dello Stato Italiano</t>
+          <t>DGS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=450c7bcccae371ea</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4353205273</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ASSISTENTE DI CANTIERE</t>
+          <t>Addetto/a selezione e valutazione del Personale</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>Adecco</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3611e110daf30aaa</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2025-05-22</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4382072576</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CONSTRUCTION PROJECT MANAGEMENT EXPERT- AVV</t>
+          <t>Talent Acquisition Trainee - Spanish &amp; Italian Market</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5754,31 +5750,31 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>internship</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=43b3e2b62c6bcaed</t>
+          <t>https://it.indeed.com/viewjob?jk=e69d1c8d88b80162</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PROGETTISTA IMPIANTI ELETTRICI</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>Zuma</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5800,24 +5796,24 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3fc4188065520f4b</t>
+          <t>https://it.indeed.com/viewjob?jk=2d4e53c8f85af891</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TRANSFORMATION EXPERT</t>
+          <t>Sommelier</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>Zuma</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5839,24 +5835,24 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=5716ffbfb20fea9e</t>
+          <t>https://it.indeed.com/viewjob?jk=f2522d0ac92e7cd8</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>DATA CENTER MANAGEMENT SENIOR</t>
+          <t>Internal AI Tools Specialist - 100% Remote - Europe</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>Hostaway</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5878,24 +5874,24 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=6bc3f5a164e56c04</t>
+          <t>https://it.indeed.com/viewjob?jk=4eff38852de5985e</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-10</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sales Assistant</t>
+          <t>Project Manager</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Il Lanificio</t>
+          <t>SEGULA Technologies</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5910,14 +5906,14 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=78eb1f40e783bd0b</t>
+          <t>https://it.indeed.com/viewjob?jk=c28fea3f09e2b064</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -5929,12 +5925,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PERSONALE ADDETTO ALLE PULIZIE</t>
+          <t>Operatore/trice Telefonia Outbound Avezzano</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>tecnocall srl</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5944,36 +5940,32 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Avezzano, ABR, IT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=25d63bac5028ffe9</t>
+          <t>https://it.indeed.com/viewjob?jk=5e3588ba0550d28f</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>HEALTH &amp; SAFETY SPECIALIST - HRI</t>
+          <t>Payroll Specialist - Roma Tor Vergata</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>SPP Agenzia per il Lavoro</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5995,24 +5987,24 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=940e37047180e47c</t>
+          <t>https://it.indeed.com/viewjob?jk=9339d90893065e7d</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PERSONALE ADDETTO AI PASSEGGERI A RIDOTTA MOBILITÀ</t>
+          <t>Addetto IT Service Desk</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Aeroporti di Roma</t>
+          <t>Poligrafico e Zecca dello Stato Italiano</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -6027,31 +6019,31 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=e15f2d9fc1729e47</t>
+          <t>https://it.indeed.com/viewjob?jk=450c7bcccae371ea</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1 Impiantista elettrico _ correnti deboli FM e BMS_ Roma _</t>
+          <t>ASSISTENTE DI CANTIERE</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Agenzia Demanio</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -6064,29 +6056,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=e9ad85d309a1d538</t>
+          <t>https://it.indeed.com/viewjob?jk=3611e110daf30aaa</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-22</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FACCHINO DI HOTEL</t>
+          <t>CONSTRUCTION PROJECT MANAGEMENT EXPERT- AVV</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Hotel Project srl</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -6108,24 +6104,24 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=49321373f510a9dc</t>
+          <t>https://it.indeed.com/viewjob?jk=43b3e2b62c6bcaed</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FACCHINO AI PIANI</t>
+          <t>PROGETTISTA IMPIANTI ELETTRICI</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Hotel Project srl</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -6147,24 +6143,24 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=a6d78c36c69724f1</t>
+          <t>https://it.indeed.com/viewjob?jk=3fc4188065520f4b</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-05-22</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Addetta/o alle pulizie Roma Sud - Zona EUR / Tintoretto/ LAURENTINA(Roma)</t>
+          <t>TRANSFORMATION EXPERT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CONSORZIO STABILE LGA SERVICE</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -6179,31 +6175,31 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=d9ea720cfa1040a9</t>
+          <t>https://it.indeed.com/viewjob?jk=5716ffbfb20fea9e</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-13</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ingegnere Civile</t>
+          <t>DATA CENTER MANAGEMENT SENIOR</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -6216,29 +6212,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=1fdf5efe88fd699b</t>
+          <t>https://it.indeed.com/viewjob?jk=6bc3f5a164e56c04</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Commerciali</t>
+          <t>Sales Assistant</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Il Lanificio</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -6251,12 +6251,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3732af90f990c3a1</t>
+          <t>https://it.indeed.com/viewjob?jk=78eb1f40e783bd0b</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -6268,12 +6272,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Montatore/trice di arredi</t>
+          <t>PERSONALE ADDETTO ALLE PULIZIE</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -6295,24 +6299,24 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=dc7f0ee00295c34c</t>
+          <t>https://it.indeed.com/viewjob?jk=25d63bac5028ffe9</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-01</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Security analyst</t>
+          <t>HEALTH &amp; SAFETY SPECIALIST - HRI</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6325,29 +6329,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=3e55262a44527bca</t>
+          <t>https://it.indeed.com/viewjob?jk=940e37047180e47c</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Specialisti IT per attività di Application Operations &amp; Support</t>
+          <t>PERSONALE ADDETTO AI PASSEGGERI A RIDOTTA MOBILITÀ</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NETwk</t>
+          <t>Aeroporti di Roma</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -6360,29 +6368,33 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f118ef9466e8c1df</t>
+          <t>https://it.indeed.com/viewjob?jk=e15f2d9fc1729e47</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Psicologo/Educatore</t>
+          <t>1 Impiantista elettrico _ correnti deboli FM e BMS_ Roma _</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AVI ONLUS</t>
+          <t>Agenzia Demanio</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6400,24 +6412,24 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=af4e37b29d92ec47</t>
+          <t>https://it.indeed.com/viewjob?jk=e9ad85d309a1d538</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Assistente domiciliare / Operatore Socio Sanitario</t>
+          <t>FACCHINO DI HOTEL</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AVI ONLUS</t>
+          <t>Hotel Project srl</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6430,12 +6442,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=aba220b330eaa455</t>
+          <t>https://it.indeed.com/viewjob?jk=49321373f510a9dc</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -6447,12 +6463,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Preposto/Referente Addette/i alle pulizie, zona Viale Libia, Roma</t>
+          <t>FACCHINO AI PIANI</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CONSORZIO STABILE LGA SERVICE</t>
+          <t>Hotel Project srl</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6474,7 +6490,7 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=363ea67eb7afb7f7</t>
+          <t>https://it.indeed.com/viewjob?jk=a6d78c36c69724f1</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -6486,10 +6502,14 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Responsabile di sala - Hotel</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr"/>
+          <t>Addetta/o alle pulizie Roma Sud - Zona EUR / Tintoretto/ LAURENTINA(Roma)</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CONSORZIO STABILE LGA SERVICE</t>
+        </is>
+      </c>
       <c r="C165" t="inlineStr">
         <is>
           <t>indeed</t>
@@ -6502,14 +6522,14 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=9860605edad9862f</t>
+          <t>https://it.indeed.com/viewjob?jk=d9ea720cfa1040a9</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -6521,12 +6541,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DISPONENTE / IMPIEGATO OPERATIVO TRASPORTI</t>
+          <t>Ingegnere Civile</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -6544,7 +6564,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=eb52cb8f26df7073</t>
+          <t>https://it.indeed.com/viewjob?jk=1fdf5efe88fd699b</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -6556,12 +6576,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Operatore Elettrotermico</t>
+          <t>Commerciali</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6579,7 +6599,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=cc8e26647237a9c8</t>
+          <t>https://it.indeed.com/viewjob?jk=3732af90f990c3a1</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -6591,12 +6611,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Addetto/a Ufficio Ordini</t>
+          <t>Montatore/trice di arredi</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -6609,12 +6629,16 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=6d0a80f9cbc435ce</t>
+          <t>https://it.indeed.com/viewjob?jk=dc7f0ee00295c34c</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -6626,7 +6650,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Assuntore/trice rischi assicurativi junior</t>
+          <t>Security analyst</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6641,7 +6665,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Latina, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -6649,7 +6673,7 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=7a232711e3a338c3</t>
+          <t>https://it.indeed.com/viewjob?jk=3e55262a44527bca</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -6661,7 +6685,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Impiegato/a Assicurativo</t>
+          <t>Specialisti IT per attività di Application Operations &amp; Support</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6676,7 +6700,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Latina, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -6684,7 +6708,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=162ff5163c37d3c5</t>
+          <t>https://it.indeed.com/viewjob?jk=f118ef9466e8c1df</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -6696,12 +6720,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Addetto/a al servizio clienti part-time</t>
+          <t>Psicologo/Educatore</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>IKEA</t>
+          <t>AVI ONLUS</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -6711,19 +6735,15 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Fiumicino, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>parttime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=ed4a3a2edfb970b5</t>
+          <t>https://it.indeed.com/viewjob?jk=af4e37b29d92ec47</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -6735,12 +6755,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Fisioterapista</t>
+          <t>Assistente domiciliare / Operatore Socio Sanitario</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Palone Rehab</t>
+          <t>AVI ONLUS</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -6750,19 +6770,15 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Lariano, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=e5323e01cd1bff45</t>
+          <t>https://it.indeed.com/viewjob?jk=aba220b330eaa455</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -6774,84 +6790,96 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HR Admin (Risorse umane)</t>
+          <t>Preposto/Referente Addette/i alle pulizie, zona Viale Libia, Roma</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Joinrs</t>
+          <t>CONSORZIO STABILE LGA SERVICE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4382957424</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=363ea67eb7afb7f7</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>People Partner, EMEA</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Trip.com Group</t>
-        </is>
-      </c>
+          <t>Responsabile di sala - Hotel</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4371369930</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=9860605edad9862f</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Impiegato/a Risorse Umane e Supporto Operativo</t>
+          <t>DISPONENTE / IMPIEGATO OPERATIVO TRASPORTI</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>tecno-system</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -6859,30 +6887,34 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4381824566</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=eb52cb8f26df7073</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Impiegato/a Risorse Umane e Gestione Presenze</t>
+          <t>Operatore Elettrotermico</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Blue consulting</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>linkedin</t>
+          <t>indeed</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Frosinone, Latium, Italy</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -6890,47 +6922,59 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4381834249</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=cc8e26647237a9c8</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HR Director - English speaker - Mandatory retail Experience</t>
+          <t>Addetto/a Ufficio Ordini</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4381729842</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=6d0a80f9cbc435ce</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
+          <t>Assuntore/trice rischi assicurativi junior</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6940,36 +6984,32 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Latina, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=f6c07b221a20019c</t>
+          <t>https://it.indeed.com/viewjob?jk=7a232711e3a338c3</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
+          <t>Impiegato/a Assicurativo</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>NETwk</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6979,36 +7019,32 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Latina, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=aad78af65d6d4a4f</t>
+          <t>https://it.indeed.com/viewjob?jk=162ff5163c37d3c5</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Business Operations Assistant and Events coordinator</t>
+          <t>Addetto/a al servizio clienti part-time</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>World Food Programme</t>
+          <t>IKEA</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -7018,19 +7054,19 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Fiumicino, LAZ, IT</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>fulltime</t>
+          <t>parttime</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=e49f076435b1d7da</t>
+          <t>https://it.indeed.com/viewjob?jk=ed4a3a2edfb970b5</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -7042,12 +7078,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Cabin Crew Application Rome Fiumicino 24 March 2026 - Evergreen</t>
+          <t>Fisioterapista</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>WIZZ AIR</t>
+          <t>Palone Rehab</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -7057,15 +7093,19 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Fiumicino, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
+          <t>Lariano, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=efe49393fd407cc0</t>
+          <t>https://it.indeed.com/viewjob?jk=e5323e01cd1bff45</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -7077,207 +7117,163 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HR Assistant L.68/99 - Categoria Protetta Part Time</t>
+          <t>HR Admin (Risorse umane)</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>BIP</t>
+          <t>Joinrs</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=de5de5a9624794c6</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>2026-03-04</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4382957424</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HR Business Partner, EU One PXT</t>
+          <t>People Partner, EMEA</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Trip.com Group</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr"/>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=638e9e675d9c4a16</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4371369930</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Addetto risorse umane</t>
+          <t>Impiegato/a Risorse Umane e Supporto Operativo</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Matrem Bakery</t>
+          <t>tecno-system</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Rome, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=14b5b53a582a0bde</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4381824566</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HR DI CANTIERE</t>
+          <t>Impiegato/a Risorse Umane e Gestione Presenze</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TEK SOLAR S.r.l.</t>
+          <t>Blue consulting</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>indeed</t>
+          <t>linkedin</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Tuscania, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Frosinone, Latium, Italy</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=d5b1e48b179d26d4</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4381834249</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Addetto/a al supporto operativo del Programma di qualificazione professionale</t>
+          <t>HR Director - English speaker - Mandatory retail Experience</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>IBIMI</t>
+          <t>Hays</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>indeed</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=30dae090e39b6123</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/jobs/view/4381729842</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HR Generalist</t>
+          <t>Area Manager, FC Operations</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>NTWK</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -7287,32 +7283,36 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr"/>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=6ce0f939d71e0143</t>
+          <t>https://it.indeed.com/viewjob?jk=f6c07b221a20019c</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-28</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Hr generalist appartenente alle categorie protette (art. 1 l. 68/99)</t>
+          <t>Military - Area Manager - Italy</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Ferrovie dello Stato Italiane</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -7322,32 +7322,36 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr"/>
+          <t>Colleferro, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=57e0925bac068957</t>
+          <t>https://it.indeed.com/viewjob?jk=aad78af65d6d4a4f</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Addetto/a Risorse Umane - Beni a largo consumo</t>
+          <t>Business Operations Assistant and Events coordinator</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>AIR</t>
+          <t>World Food Programme</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -7369,7 +7373,7 @@
       <c r="G189" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=41c9d6384754830b</t>
+          <t>https://it.indeed.com/viewjob?jk=e49f076435b1d7da</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -7381,12 +7385,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Addetto/a Ufficio Risorse Umane – Grande Distribuzione Organizzata</t>
+          <t>Cabin Crew Application Rome Fiumicino 24 March 2026 - Evergreen</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Novati</t>
+          <t>WIZZ AIR</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -7396,19 +7400,15 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Terni, UMB, IT</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Fiumicino, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=729a652ae9cb014d</t>
+          <t>https://it.indeed.com/viewjob?jk=efe49393fd407cc0</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -7420,39 +7420,51 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Talent Acquisition Manager - Retail GDO</t>
+          <t>HR Assistant L.68/99 - Categoria Protetta Part Time</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Hays</t>
+          <t>BIP</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>linkedin</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4381729939</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
+          <t>https://it.indeed.com/viewjob?jk=de5de5a9624794c6</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Conferimento dell'incarico quinquennale di direttore della U.O.C. Anestesia e rianimazione Presidio ospedaliero P. Colombo di Velletri.</t>
+          <t>HR Business Partner, EU One PXT</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>AZIENDA SANITARIA LOCALE ROMA 6 - ALBANO LAZIALE</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -7462,32 +7474,36 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Albano Laziale, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr"/>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=827f392308390891</t>
+          <t>https://it.indeed.com/viewjob?jk=638e9e675d9c4a16</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Promoter/Hostess</t>
+          <t>Addetto risorse umane</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Oserot</t>
+          <t>Matrem Bakery</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -7502,31 +7518,31 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>parttime, fulltime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=56a7004ccbac5fc3</t>
+          <t>https://it.indeed.com/viewjob?jk=14b5b53a582a0bde</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PERSONALE ADDETTO PULIZIE PART TIME CENTRO FITNESS GORDIANI</t>
+          <t>HR DI CANTIERE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Corefit srl</t>
+          <t>TEK SOLAR S.r.l.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -7536,36 +7552,36 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Roma, LAZ, IT</t>
+          <t>Tuscania, LAZ, IT</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>parttime</t>
+          <t>fulltime</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=09d2cee30c11abad</t>
+          <t>https://it.indeed.com/viewjob?jk=d5b1e48b179d26d4</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Area Manager, FC Operations</t>
+          <t>Addetto/a al supporto operativo del Programma di qualificazione professionale</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>IBIMI</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7575,7 +7591,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Passo Corese, LAZ, IT</t>
+          <t>Roma, LAZ, IT</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7587,24 +7603,24 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=cbe8a695fef1d8f4</t>
+          <t>https://it.indeed.com/viewjob?jk=30dae090e39b6123</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Military - Area Manager - Italy</t>
+          <t>HR Generalist</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -7614,36 +7630,32 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Colleferro, LAZ, IT</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>https://it.indeed.com/viewjob?jk=a8df3f8a0a6a769a</t>
+          <t>https://it.indeed.com/viewjob?jk=6ce0f939d71e0143</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>HR Business Partner, EU One PXT</t>
+          <t>Hr generalist appartenente alle categorie protette (art. 1 l. 68/99)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>Ferrovie dello Stato Italiane</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7656,26 +7668,357 @@
           <t>Roma, LAZ, IT</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>fulltime</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
+          <t>https://it.indeed.com/viewjob?jk=57e0925bac068957</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Addetto/a Risorse Umane - Beni a largo consumo</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>AIR</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=41c9d6384754830b</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Addetto/a Ufficio Risorse Umane – Grande Distribuzione Organizzata</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Novati</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Terni, UMB, IT</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=729a652ae9cb014d</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Talent Acquisition Manager - Retail GDO</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Hays</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>linkedin</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4381729939</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Conferimento dell'incarico quinquennale di direttore della U.O.C. Anestesia e rianimazione Presidio ospedaliero P. Colombo di Velletri.</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>AZIENDA SANITARIA LOCALE ROMA 6 - ALBANO LAZIALE</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Albano Laziale, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=827f392308390891</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Promoter/Hostess</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Oserot</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>parttime, fulltime</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=56a7004ccbac5fc3</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PERSONALE ADDETTO PULIZIE PART TIME CENTRO FITNESS GORDIANI</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Corefit srl</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>parttime</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=09d2cee30c11abad</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Area Manager, FC Operations</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Passo Corese, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=cbe8a695fef1d8f4</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Military - Area Manager - Italy</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Colleferro, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>https://it.indeed.com/viewjob?jk=a8df3f8a0a6a769a</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>HR Business Partner, EU One PXT</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Amazon.com</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>indeed</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Roma, LAZ, IT</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>fulltime</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
           <t>https://it.indeed.com/viewjob?jk=b03601db7a89485b</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I206" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I197"/>
+  <autoFilter ref="A1:I206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>